--- a/00_Data/Monkey/Parameters.xlsx
+++ b/00_Data/Monkey/Parameters.xlsx
@@ -1,27 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KrinaMehta\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5D8EF8-E327-4055-A58D-35E56252756B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Included" sheetId="1" r:id="rId1"/>
-    <sheet name="Additional" sheetId="2" r:id="rId2"/>
+    <sheet name="Included" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Additional" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
   <si>
     <t>Drug Name</t>
   </si>
@@ -282,19 +275,28 @@
   </si>
   <si>
     <t>Benamara et al., 2026; PMID: 41536283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/min</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -319,8 +321,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -602,20 +604,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="23.1796875" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="18.54296875" customWidth="1"/>
-    <col min="5" max="5" width="10.26953125" customWidth="1"/>
-    <col min="6" max="6" width="42" customWidth="1"/>
-    <col min="7" max="7" width="60" customWidth="1"/>
+    <col min="1" max="1" width="23.1796875" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="32" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="18.54296875" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="10.26953125" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="42" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="60" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -638,7 +640,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -648,7 +650,7 @@
       <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>0.65</v>
       </c>
       <c r="E2" t="s">
@@ -661,7 +663,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" ht="29" customHeight="1">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -671,8 +673,8 @@
       <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="D3">
-        <v>0.29899999999999999</v>
+      <c r="D3" t="n">
+        <v>0.000299</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -684,7 +686,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -694,7 +696,7 @@
       <c r="C4" t="s">
         <v>15</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>9.3600000000000003E-3</v>
       </c>
       <c r="E4" t="s">
@@ -707,7 +709,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" ht="29" customHeight="1">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -717,7 +719,7 @@
       <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>0.60599999999999998</v>
       </c>
       <c r="E5" t="s">
@@ -730,7 +732,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -740,7 +742,7 @@
       <c r="C6" t="s">
         <v>20</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>0.60899999999999999</v>
       </c>
       <c r="E6" t="s">
@@ -753,7 +755,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -763,7 +765,7 @@
       <c r="C7" t="s">
         <v>23</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>4.2599999999999999E-2</v>
       </c>
       <c r="E7" t="s">
@@ -776,7 +778,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -786,7 +788,7 @@
       <c r="C8" t="s">
         <v>9</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>1.07</v>
       </c>
       <c r="E8" t="s">
@@ -799,7 +801,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -809,7 +811,7 @@
       <c r="C9" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="1" t="n">
         <v>4.6699999999999997E-5</v>
       </c>
       <c r="E9" t="s">
@@ -822,7 +824,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -832,7 +834,7 @@
       <c r="C10" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="1" t="n">
         <v>1.74E-3</v>
       </c>
       <c r="E10" t="s">
@@ -845,7 +847,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -855,7 +857,7 @@
       <c r="C11" t="s">
         <v>17</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>0.25</v>
       </c>
       <c r="E11" t="s">
@@ -868,7 +870,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -878,7 +880,7 @@
       <c r="C12" t="s">
         <v>20</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>0.60899999999999999</v>
       </c>
       <c r="E12" t="s">
@@ -891,7 +893,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" ht="29" customHeight="1">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -901,7 +903,7 @@
       <c r="C13" t="s">
         <v>23</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="n">
         <v>4.2599999999999999E-2</v>
       </c>
       <c r="E13" t="s">
@@ -914,7 +916,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -924,7 +926,7 @@
       <c r="C14" t="s">
         <v>9</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="n">
         <v>1.07</v>
       </c>
       <c r="E14" t="s">
@@ -937,7 +939,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" ht="29" customHeight="1">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -947,7 +949,7 @@
       <c r="C15" t="s">
         <v>13</v>
       </c>
-      <c r="D15">
+      <c r="D15" t="n">
         <v>1.4499999999999999E-3</v>
       </c>
       <c r="E15" t="s">
@@ -960,7 +962,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" ht="29" customHeight="1">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -970,11 +972,11 @@
       <c r="C16" t="s">
         <v>15</v>
       </c>
-      <c r="D16">
+      <c r="D16" t="n">
         <v>0.114</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>35</v>
@@ -983,7 +985,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" ht="29" customHeight="1">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -993,7 +995,7 @@
       <c r="C17" t="s">
         <v>17</v>
       </c>
-      <c r="D17">
+      <c r="D17" t="n">
         <v>2.7E-2</v>
       </c>
       <c r="E17" t="s">
@@ -1006,7 +1008,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" ht="29" customHeight="1">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -1016,7 +1018,7 @@
       <c r="C18" t="s">
         <v>20</v>
       </c>
-      <c r="D18">
+      <c r="D18" t="n">
         <v>1.66E-2</v>
       </c>
       <c r="E18" t="s">
@@ -1029,7 +1031,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" ht="29" customHeight="1">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -1039,7 +1041,7 @@
       <c r="C19" t="s">
         <v>23</v>
       </c>
-      <c r="D19">
+      <c r="D19" t="n">
         <v>2.7E-2</v>
       </c>
       <c r="E19" t="s">
@@ -1052,7 +1054,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20">
       <c r="A20" t="s">
         <v>40</v>
       </c>
@@ -1062,7 +1064,7 @@
       <c r="C20" t="s">
         <v>9</v>
       </c>
-      <c r="D20">
+      <c r="D20" t="n">
         <v>8.1000000000000003E-2</v>
       </c>
       <c r="E20" t="s">
@@ -1075,7 +1077,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -1085,7 +1087,7 @@
       <c r="C21" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" s="1" t="n">
         <v>3.1E-4</v>
       </c>
       <c r="E21" t="s">
@@ -1098,7 +1100,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -1108,7 +1110,7 @@
       <c r="C22" t="s">
         <v>15</v>
       </c>
-      <c r="D22">
+      <c r="D22" t="n">
         <v>1.6999999999999999E-3</v>
       </c>
       <c r="E22" t="s">
@@ -1121,7 +1123,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -1131,7 +1133,7 @@
       <c r="C23" t="s">
         <v>17</v>
       </c>
-      <c r="D23">
+      <c r="D23" t="n">
         <v>2.7E-2</v>
       </c>
       <c r="F23" s="2" t="s">
@@ -1141,7 +1143,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -1151,7 +1153,7 @@
       <c r="C24" t="s">
         <v>20</v>
       </c>
-      <c r="D24">
+      <c r="D24" t="n">
         <v>1.66E-2</v>
       </c>
       <c r="E24" t="s">
@@ -1164,7 +1166,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -1174,7 +1176,7 @@
       <c r="C25" t="s">
         <v>23</v>
       </c>
-      <c r="D25">
+      <c r="D25" t="n">
         <v>2.7E-2</v>
       </c>
       <c r="E25" t="s">
@@ -1187,7 +1189,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26">
       <c r="A26" t="s">
         <v>42</v>
       </c>
@@ -1197,7 +1199,7 @@
       <c r="C26" t="s">
         <v>9</v>
       </c>
-      <c r="D26">
+      <c r="D26" t="n">
         <v>1.07</v>
       </c>
       <c r="E26" t="s">
@@ -1210,7 +1212,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" ht="29" customHeight="1">
       <c r="A27" t="s">
         <v>42</v>
       </c>
@@ -1220,7 +1222,7 @@
       <c r="C27" t="s">
         <v>13</v>
       </c>
-      <c r="D27">
+      <c r="D27" t="n">
         <v>5.8E-5</v>
       </c>
       <c r="E27" t="s">
@@ -1233,7 +1235,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" ht="29" customHeight="1">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -1243,7 +1245,7 @@
       <c r="C28" t="s">
         <v>15</v>
       </c>
-      <c r="D28">
+      <c r="D28" t="n">
         <v>1.8600000000000001E-3</v>
       </c>
       <c r="E28" t="s">
@@ -1256,7 +1258,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29">
       <c r="A29" t="s">
         <v>42</v>
       </c>
@@ -1266,7 +1268,7 @@
       <c r="C29" t="s">
         <v>17</v>
       </c>
-      <c r="D29">
+      <c r="D29" t="n">
         <v>0.48</v>
       </c>
       <c r="E29" t="s">
@@ -1279,7 +1281,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30">
       <c r="A30" t="s">
         <v>42</v>
       </c>
@@ -1289,7 +1291,7 @@
       <c r="C30" t="s">
         <v>20</v>
       </c>
-      <c r="D30">
+      <c r="D30" t="n">
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="E30" t="s">
@@ -1302,7 +1304,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -1312,7 +1314,7 @@
       <c r="C31" t="s">
         <v>23</v>
       </c>
-      <c r="D31">
+      <c r="D31" t="n">
         <v>0.48</v>
       </c>
       <c r="E31" t="s">
@@ -1323,7 +1325,7 @@
       </c>
       <c r="G31" s="2"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32">
       <c r="A32" t="s">
         <v>49</v>
       </c>
@@ -1333,7 +1335,7 @@
       <c r="C32" t="s">
         <v>9</v>
       </c>
-      <c r="D32">
+      <c r="D32" t="n">
         <v>1.07</v>
       </c>
       <c r="E32" t="s">
@@ -1346,7 +1348,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33">
       <c r="A33" t="s">
         <v>49</v>
       </c>
@@ -1356,7 +1358,7 @@
       <c r="C33" t="s">
         <v>13</v>
       </c>
-      <c r="D33">
+      <c r="D33" t="n">
         <v>1.34E-3</v>
       </c>
       <c r="E33" t="s">
@@ -1369,7 +1371,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34">
       <c r="A34" t="s">
         <v>49</v>
       </c>
@@ -1379,7 +1381,7 @@
       <c r="C34" t="s">
         <v>15</v>
       </c>
-      <c r="D34">
+      <c r="D34" t="n">
         <v>1.2840000000000001E-2</v>
       </c>
       <c r="E34" t="s">
@@ -1392,7 +1394,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35">
       <c r="A35" t="s">
         <v>49</v>
       </c>
@@ -1402,7 +1404,7 @@
       <c r="C35" t="s">
         <v>17</v>
       </c>
-      <c r="D35">
+      <c r="D35" t="n">
         <v>0.28000000000000003</v>
       </c>
       <c r="E35" t="s">
@@ -1415,7 +1417,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36">
       <c r="A36" t="s">
         <v>49</v>
       </c>
@@ -1425,7 +1427,7 @@
       <c r="C36" t="s">
         <v>20</v>
       </c>
-      <c r="D36">
+      <c r="D36" t="n">
         <v>2.2000000000000002</v>
       </c>
       <c r="E36" t="s">
@@ -1438,7 +1440,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37">
       <c r="A37" t="s">
         <v>49</v>
       </c>
@@ -1448,7 +1450,7 @@
       <c r="C37" t="s">
         <v>23</v>
       </c>
-      <c r="D37">
+      <c r="D37" t="n">
         <v>0.28000000000000003</v>
       </c>
       <c r="E37" t="s">
@@ -1461,7 +1463,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38">
       <c r="A38" t="s">
         <v>56</v>
       </c>
@@ -1471,7 +1473,7 @@
       <c r="C38" t="s">
         <v>9</v>
       </c>
-      <c r="D38">
+      <c r="D38" t="n">
         <v>1.07</v>
       </c>
       <c r="E38" t="s">
@@ -1484,7 +1486,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39">
       <c r="A39" t="s">
         <v>56</v>
       </c>
@@ -1494,7 +1496,7 @@
       <c r="C39" t="s">
         <v>13</v>
       </c>
-      <c r="D39">
+      <c r="D39" t="n">
         <v>1.27E-4</v>
       </c>
       <c r="E39" t="s">
@@ -1507,7 +1509,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40">
       <c r="A40" t="s">
         <v>56</v>
       </c>
@@ -1517,7 +1519,7 @@
       <c r="C40" t="s">
         <v>15</v>
       </c>
-      <c r="D40">
+      <c r="D40" t="n">
         <v>9.5999999999999992E-3</v>
       </c>
       <c r="E40" t="s">
@@ -1530,7 +1532,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41">
       <c r="A41" t="s">
         <v>56</v>
       </c>
@@ -1540,7 +1542,7 @@
       <c r="C41" t="s">
         <v>17</v>
       </c>
-      <c r="D41">
+      <c r="D41" t="n">
         <v>0.86599999999999999</v>
       </c>
       <c r="E41" t="s">
@@ -1553,7 +1555,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42">
       <c r="A42" t="s">
         <v>56</v>
       </c>
@@ -1563,7 +1565,7 @@
       <c r="C42" t="s">
         <v>20</v>
       </c>
-      <c r="D42">
+      <c r="D42" t="n">
         <v>1E-3</v>
       </c>
       <c r="E42" t="s">
@@ -1576,7 +1578,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43">
       <c r="A43" t="s">
         <v>56</v>
       </c>
@@ -1586,7 +1588,7 @@
       <c r="C43" t="s">
         <v>23</v>
       </c>
-      <c r="D43">
+      <c r="D43" t="n">
         <v>0.223</v>
       </c>
       <c r="E43" t="s">
@@ -1599,7 +1601,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44">
       <c r="A44" t="s">
         <v>65</v>
       </c>
@@ -1609,7 +1611,7 @@
       <c r="C44" t="s">
         <v>9</v>
       </c>
-      <c r="D44">
+      <c r="D44" t="n">
         <v>1.07</v>
       </c>
       <c r="E44" t="s">
@@ -1622,7 +1624,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="45">
       <c r="A45" t="s">
         <v>65</v>
       </c>
@@ -1632,7 +1634,7 @@
       <c r="C45" t="s">
         <v>13</v>
       </c>
-      <c r="D45">
+      <c r="D45" t="n">
         <v>1.8E-5</v>
       </c>
       <c r="E45" t="s">
@@ -1645,7 +1647,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46">
       <c r="A46" t="s">
         <v>65</v>
       </c>
@@ -1655,7 +1657,7 @@
       <c r="C46" t="s">
         <v>15</v>
       </c>
-      <c r="D46">
+      <c r="D46" t="n">
         <v>5.5830000000000003E-3</v>
       </c>
       <c r="E46" t="s">
@@ -1668,7 +1670,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47">
       <c r="A47" t="s">
         <v>65</v>
       </c>
@@ -1678,7 +1680,7 @@
       <c r="C47" t="s">
         <v>17</v>
       </c>
-      <c r="D47">
+      <c r="D47" t="n">
         <v>0.86599999999999999</v>
       </c>
       <c r="E47" t="s">
@@ -1691,7 +1693,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48">
       <c r="A48" t="s">
         <v>65</v>
       </c>
@@ -1701,7 +1703,7 @@
       <c r="C48" t="s">
         <v>20</v>
       </c>
-      <c r="D48">
+      <c r="D48" t="n">
         <v>1E-3</v>
       </c>
       <c r="E48" t="s">
@@ -1714,7 +1716,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49">
       <c r="A49" t="s">
         <v>65</v>
       </c>
@@ -1724,7 +1726,7 @@
       <c r="C49" t="s">
         <v>23</v>
       </c>
-      <c r="D49">
+      <c r="D49" t="n">
         <v>0.223</v>
       </c>
       <c r="E49" t="s">
@@ -1744,11 +1746,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" ht="29" customHeight="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1771,7 +1773,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" ht="29" customHeight="1">
       <c r="A2" t="s">
         <v>68</v>
       </c>
@@ -1781,7 +1783,7 @@
       <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>0.63</v>
       </c>
       <c r="E2" t="s">
@@ -1794,7 +1796,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" ht="29" customHeight="1">
       <c r="A3" t="s">
         <v>68</v>
       </c>
@@ -1804,7 +1806,7 @@
       <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>9.8999999999999999E-4</v>
       </c>
       <c r="E3" t="s">
@@ -1817,7 +1819,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" ht="29" customHeight="1">
       <c r="A4" t="s">
         <v>68</v>
       </c>
@@ -1827,7 +1829,7 @@
       <c r="C4" t="s">
         <v>15</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>0.05</v>
       </c>
       <c r="E4" t="s">
@@ -1840,7 +1842,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" ht="29" customHeight="1">
       <c r="A5" t="s">
         <v>68</v>
       </c>
@@ -1850,7 +1852,7 @@
       <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>0.12</v>
       </c>
       <c r="E5" t="s">
@@ -1863,7 +1865,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" ht="29" customHeight="1">
       <c r="A6" t="s">
         <v>68</v>
       </c>
@@ -1873,7 +1875,7 @@
       <c r="C6" t="s">
         <v>20</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="E6" t="s">
@@ -1886,7 +1888,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" ht="43.5" customHeight="1">
       <c r="A7" t="s">
         <v>68</v>
       </c>
@@ -1896,7 +1898,7 @@
       <c r="C7" t="s">
         <v>23</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>0.12</v>
       </c>
       <c r="F7" s="2" t="s">
@@ -1906,7 +1908,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" ht="58" customHeight="1">
       <c r="A8" t="s">
         <v>75</v>
       </c>
@@ -1916,7 +1918,7 @@
       <c r="C8" t="s">
         <v>9</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>1.05</v>
       </c>
       <c r="E8" t="s">
@@ -1929,7 +1931,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" ht="29" customHeight="1">
       <c r="A9" t="s">
         <v>75</v>
       </c>
@@ -1939,7 +1941,7 @@
       <c r="C9" t="s">
         <v>13</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>4.6E-5</v>
       </c>
       <c r="E9" t="s">
@@ -1952,7 +1954,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" ht="29" customHeight="1">
       <c r="A10" t="s">
         <v>75</v>
       </c>
@@ -1962,7 +1964,7 @@
       <c r="C10" t="s">
         <v>15</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>4.3800000000000002E-4</v>
       </c>
       <c r="E10" t="s">
@@ -1975,7 +1977,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="87" x14ac:dyDescent="0.35">
+    <row r="11" ht="87" customHeight="1">
       <c r="A11" t="s">
         <v>75</v>
       </c>
@@ -1985,7 +1987,7 @@
       <c r="C11" t="s">
         <v>17</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>0.48</v>
       </c>
       <c r="E11" t="s">
@@ -1998,7 +2000,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="87" x14ac:dyDescent="0.35">
+    <row r="12" ht="87" customHeight="1">
       <c r="A12" t="s">
         <v>75</v>
       </c>
@@ -2008,7 +2010,7 @@
       <c r="C12" t="s">
         <v>20</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="E12" t="s">
@@ -2021,7 +2023,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="87" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" ht="87" customHeight="1">
       <c r="A13" t="s">
         <v>75</v>
       </c>
@@ -2031,7 +2033,7 @@
       <c r="C13" t="s">
         <v>23</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="n">
         <v>0.48</v>
       </c>
       <c r="E13" t="s">
@@ -2044,7 +2046,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="14" ht="58" customHeight="1">
       <c r="A14" t="s">
         <v>78</v>
       </c>
@@ -2054,7 +2056,7 @@
       <c r="C14" t="s">
         <v>9</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="n">
         <v>1.05</v>
       </c>
       <c r="E14" t="s">
@@ -2067,7 +2069,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" ht="72.5" customHeight="1">
       <c r="A15" t="s">
         <v>78</v>
       </c>
@@ -2090,7 +2092,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" ht="72.5" customHeight="1">
       <c r="A16" t="s">
         <v>78</v>
       </c>
@@ -2113,7 +2115,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" ht="72.5" customHeight="1">
       <c r="A17" t="s">
         <v>78</v>
       </c>
@@ -2123,7 +2125,7 @@
       <c r="C17" t="s">
         <v>17</v>
       </c>
-      <c r="D17">
+      <c r="D17" t="n">
         <v>0.28000000000000003</v>
       </c>
       <c r="E17" t="s">
@@ -2136,7 +2138,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" ht="72.5" customHeight="1">
       <c r="A18" t="s">
         <v>78</v>
       </c>
@@ -2146,7 +2148,7 @@
       <c r="C18" t="s">
         <v>20</v>
       </c>
-      <c r="D18">
+      <c r="D18" t="n">
         <v>2.2000000000000002</v>
       </c>
       <c r="E18" t="s">
@@ -2159,7 +2161,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" ht="72.5" customHeight="1">
       <c r="A19" t="s">
         <v>78</v>
       </c>
@@ -2169,7 +2171,7 @@
       <c r="C19" t="s">
         <v>23</v>
       </c>
-      <c r="D19">
+      <c r="D19" t="n">
         <v>0.28000000000000003</v>
       </c>
       <c r="E19" t="s">
@@ -2184,5 +2186,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>